--- a/Result/profitability/2612.xlsx
+++ b/Result/profitability/2612.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.57</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7275</v>
+        <v>1.84125</v>
       </c>
       <c r="N2" t="n">
-        <v>34.5275</v>
+        <v>36.03875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.91</v>
       </c>
       <c r="M3" t="n">
-        <v>2.1425</v>
+        <v>1.96</v>
       </c>
       <c r="N3" t="n">
-        <v>38.53375</v>
+        <v>39.59625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>4.58</v>
       </c>
       <c r="M4" t="n">
-        <v>2.345</v>
+        <v>2.38125</v>
       </c>
       <c r="N4" t="n">
-        <v>42.5475</v>
+        <v>43.3575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75625</v>
+        <v>2.71375</v>
       </c>
       <c r="N5" t="n">
-        <v>46.6475</v>
+        <v>47.355</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>3.78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.99875</v>
+        <v>3.04125</v>
       </c>
       <c r="N6" t="n">
-        <v>50.485</v>
+        <v>51.0175</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>3.54</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29625</v>
+        <v>3.3275</v>
       </c>
       <c r="N7" t="n">
-        <v>53.235</v>
+        <v>53.68625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.48375</v>
+        <v>3.51625</v>
       </c>
       <c r="N8" t="n">
-        <v>54.28375</v>
+        <v>54.825</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>3.25125</v>
       </c>
       <c r="N10" t="n">
-        <v>54.55625000000001</v>
+        <v>54.55625</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D75" t="n">
+        <v>835</v>
+      </c>
+      <c r="E75" t="n">
+        <v>506</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>373</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>27.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J75" t="n">
+        <v>341</v>
+      </c>
+      <c r="K75" t="n">
+        <v>296</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.46875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.10375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1296795447738843</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3400000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1847826086956522</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.659999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1765439800374298</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
